--- a/dist/tally_templates/DPRT.xlsx
+++ b/dist/tally_templates/DPRT.xlsx
@@ -1169,7 +1169,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -2690,7 +2690,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="556">
+  <cellXfs count="596">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4344,6 +4344,126 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4352,11 +4472,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4624,7 +4744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y138"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -5386,14 +5506,14 @@
       <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="158" t="s">
+      <c r="E7" s="138" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="158"/>
       <c r="G7" s="269" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="176">
+      <c r="H7" s="572">
         <v>46227</v>
       </c>
       <c r="I7" s="158"/>
@@ -5423,14 +5543,14 @@
       <c r="D8" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="158">
+      <c r="E8" s="138">
         <v>8</v>
       </c>
       <c r="F8" s="158"/>
       <c r="G8" s="269" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="158" t="s">
+      <c r="H8" s="138" t="s">
         <v>106</v>
       </c>
       <c r="I8" s="158"/>
@@ -6659,14 +6779,14 @@
       <c r="D52" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="158" t="s">
+      <c r="E52" s="138" t="s">
         <v>117</v>
       </c>
       <c r="F52" s="158"/>
       <c r="G52" s="269" t="s">
         <v>5</v>
       </c>
-      <c r="H52" s="176">
+      <c r="H52" s="572">
         <v>46063</v>
       </c>
       <c r="I52" s="158"/>
@@ -6696,14 +6816,14 @@
       <c r="D53" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="158">
+      <c r="E53" s="138">
         <v>6</v>
       </c>
       <c r="F53" s="158"/>
       <c r="G53" s="269" t="s">
         <v>8</v>
       </c>
-      <c r="H53" s="158" t="s">
+      <c r="H53" s="138" t="s">
         <v>106</v>
       </c>
       <c r="I53" s="158"/>
@@ -8048,14 +8168,14 @@
       <c r="D96" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E96" s="158" t="s">
+      <c r="E96" s="138" t="s">
         <v>77</v>
       </c>
       <c r="F96" s="158"/>
       <c r="G96" s="269" t="s">
         <v>5</v>
       </c>
-      <c r="H96" s="176">
+      <c r="H96" s="572">
         <v>46228</v>
       </c>
       <c r="I96" s="158"/>
@@ -8085,14 +8205,14 @@
       <c r="D97" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="E97" s="158">
+      <c r="E97" s="138">
         <v>8</v>
       </c>
       <c r="F97" s="158"/>
       <c r="G97" s="269" t="s">
         <v>8</v>
       </c>
-      <c r="H97" s="158" t="s">
+      <c r="H97" s="138" t="s">
         <v>106</v>
       </c>
       <c r="I97" s="158"/>
@@ -8217,27 +8337,17 @@
       <c r="Y100" s="1"/>
     </row>
     <row r="101" ht="21" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A101" s="325" t="s">
-        <v>134</v>
-      </c>
+      <c r="A101" s="325"/>
       <c r="B101" s="323"/>
-      <c r="C101" s="323" t="s">
-        <v>119</v>
-      </c>
+      <c r="C101" s="323"/>
       <c r="D101" s="184"/>
       <c r="E101" s="185"/>
-      <c r="F101" s="372">
-        <v>-18</v>
-      </c>
-      <c r="G101" s="372">
-        <v>-15.3</v>
-      </c>
+      <c r="F101" s="372"/>
+      <c r="G101" s="372"/>
       <c r="H101" s="373" t="s">
         <v>135</v>
       </c>
-      <c r="I101" s="323" t="s">
-        <v>136</v>
-      </c>
+      <c r="I101" s="323"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -8256,27 +8366,15 @@
       <c r="Y101" s="1"/>
     </row>
     <row r="102" ht="21" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A102" s="400" t="s">
-        <v>137</v>
-      </c>
+      <c r="A102" s="400"/>
       <c r="B102" s="329"/>
-      <c r="C102" s="329" t="s">
-        <v>119</v>
-      </c>
+      <c r="C102" s="329"/>
       <c r="D102" s="139"/>
       <c r="E102" s="146"/>
-      <c r="F102" s="376">
-        <v>-18</v>
-      </c>
-      <c r="G102" s="376">
-        <v>-10.7</v>
-      </c>
-      <c r="H102" s="401" t="s">
-        <v>122</v>
-      </c>
-      <c r="I102" s="329" t="s">
-        <v>136</v>
-      </c>
+      <c r="F102" s="376"/>
+      <c r="G102" s="376"/>
+      <c r="H102" s="401"/>
+      <c r="I102" s="329"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -8295,27 +8393,15 @@
       <c r="Y102" s="1"/>
     </row>
     <row r="103" ht="21" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A103" s="400" t="s">
-        <v>138</v>
-      </c>
+      <c r="A103" s="400"/>
       <c r="B103" s="329"/>
-      <c r="C103" s="329" t="s">
-        <v>119</v>
-      </c>
+      <c r="C103" s="329"/>
       <c r="D103" s="139"/>
       <c r="E103" s="146"/>
-      <c r="F103" s="376">
-        <v>-18</v>
-      </c>
-      <c r="G103" s="376">
-        <v>-9.4</v>
-      </c>
-      <c r="H103" s="401" t="s">
-        <v>122</v>
-      </c>
-      <c r="I103" s="329" t="s">
-        <v>136</v>
-      </c>
+      <c r="F103" s="376"/>
+      <c r="G103" s="376"/>
+      <c r="H103" s="401"/>
+      <c r="I103" s="329"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -8334,27 +8420,15 @@
       <c r="Y103" s="1"/>
     </row>
     <row r="104" ht="21" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A104" s="400" t="s">
-        <v>139</v>
-      </c>
+      <c r="A104" s="400"/>
       <c r="B104" s="329"/>
-      <c r="C104" s="329" t="s">
-        <v>119</v>
-      </c>
+      <c r="C104" s="329"/>
       <c r="D104" s="139"/>
       <c r="E104" s="146"/>
-      <c r="F104" s="376">
-        <v>-18</v>
-      </c>
-      <c r="G104" s="376">
-        <v>-10.6</v>
-      </c>
-      <c r="H104" s="401" t="s">
-        <v>122</v>
-      </c>
-      <c r="I104" s="329" t="s">
-        <v>136</v>
-      </c>
+      <c r="F104" s="376"/>
+      <c r="G104" s="376"/>
+      <c r="H104" s="401"/>
+      <c r="I104" s="329"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -8373,27 +8447,15 @@
       <c r="Y104" s="1"/>
     </row>
     <row r="105" ht="21" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A105" s="402" t="s">
-        <v>140</v>
-      </c>
+      <c r="A105" s="402"/>
       <c r="B105" s="334"/>
-      <c r="C105" s="334" t="s">
-        <v>119</v>
-      </c>
+      <c r="C105" s="334"/>
       <c r="D105" s="148"/>
       <c r="E105" s="149"/>
-      <c r="F105" s="393">
-        <v>-18</v>
-      </c>
-      <c r="G105" s="393">
-        <v>-8.5</v>
-      </c>
-      <c r="H105" s="403" t="s">
-        <v>122</v>
-      </c>
-      <c r="I105" s="334" t="s">
-        <v>136</v>
-      </c>
+      <c r="F105" s="393"/>
+      <c r="G105" s="393"/>
+      <c r="H105" s="403"/>
+      <c r="I105" s="334"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -9424,7 +9486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10154,7 +10216,7 @@
       <c r="A6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="175" t="s">
+      <c r="B6" s="138" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -10166,7 +10228,7 @@
         <v>62</v>
       </c>
       <c r="I6" s="158"/>
-      <c r="J6" s="158" t="s">
+      <c r="J6" s="138" t="s">
         <v>77</v>
       </c>
       <c r="K6" s="158"/>
@@ -10176,7 +10238,7 @@
       <c r="O6" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="P6" s="176">
+      <c r="P6" s="572">
         <v>46228</v>
       </c>
       <c r="Q6" s="158"/>
@@ -10220,7 +10282,7 @@
       <c r="A8" s="175" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="175" t="s">
+      <c r="B8" s="138" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="175"/>
@@ -10232,7 +10294,7 @@
         <v>66</v>
       </c>
       <c r="I8" s="158"/>
-      <c r="J8" s="158" t="s">
+      <c r="J8" s="138" t="s">
         <v>67</v>
       </c>
       <c r="K8" s="158"/>
@@ -10242,7 +10304,7 @@
       <c r="O8" s="175" t="s">
         <v>78</v>
       </c>
-      <c r="P8" s="158">
+      <c r="P8" s="138">
         <v>8</v>
       </c>
       <c r="Q8" s="158"/>
@@ -10282,7 +10344,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="179" t="s">
         <v>11</v>
       </c>
@@ -10323,7 +10385,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="182"/>
       <c r="B11" s="182"/>
       <c r="C11" s="235"/>
@@ -11139,7 +11201,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -11869,7 +11931,7 @@
       <c r="A6" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="175" t="s">
+      <c r="B6" s="138" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -11881,7 +11943,7 @@
         <v>62</v>
       </c>
       <c r="I6" s="158"/>
-      <c r="J6" s="158" t="s">
+      <c r="J6" s="138" t="s">
         <v>63</v>
       </c>
       <c r="K6" s="158"/>
@@ -11891,7 +11953,7 @@
       <c r="O6" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="P6" s="176">
+      <c r="P6" s="572">
         <v>46227</v>
       </c>
       <c r="Q6" s="158"/>
@@ -11935,7 +11997,7 @@
       <c r="A8" s="175" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="175" t="s">
+      <c r="B8" s="138" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="175"/>
@@ -11947,7 +12009,7 @@
         <v>66</v>
       </c>
       <c r="I8" s="158"/>
-      <c r="J8" s="158" t="s">
+      <c r="J8" s="138" t="s">
         <v>67</v>
       </c>
       <c r="K8" s="158"/>
@@ -11957,7 +12019,7 @@
       <c r="O8" s="175" t="s">
         <v>68</v>
       </c>
-      <c r="P8" s="158">
+      <c r="P8" s="138">
         <v>8</v>
       </c>
       <c r="Q8" s="158"/>
@@ -11997,7 +12059,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="177" t="s">
         <v>11</v>
       </c>
@@ -12038,7 +12100,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="180"/>
       <c r="C11" s="235"/>
@@ -12852,7 +12914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF333300"/>
   </sheetPr>
@@ -13147,7 +13209,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -13207,7 +13269,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="556" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -13216,13 +13278,13 @@
       <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="557"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="558"/>
       <c r="L4" s="12"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -13269,20 +13331,20 @@
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="13"/>
+      <c r="B6" s="557"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="557"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="558"/>
       <c r="L6" s="15" t="s">
         <v>9</v>
       </c>
@@ -14988,7 +15050,7 @@
       <c r="X63" s="35"/>
       <c r="Y63" s="35"/>
     </row>
-    <row r="64" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="44"/>
       <c r="B64" s="63"/>
       <c r="C64" s="73" t="s">
@@ -15017,7 +15079,7 @@
       <c r="X64" s="35"/>
       <c r="Y64" s="35"/>
     </row>
-    <row r="65" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="44"/>
       <c r="B65" s="45"/>
       <c r="C65" s="46" t="s">
@@ -15046,7 +15108,7 @@
       <c r="X65" s="35"/>
       <c r="Y65" s="35"/>
     </row>
-    <row r="66" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="44"/>
       <c r="B66" s="52"/>
       <c r="C66" s="46" t="s">
@@ -15075,7 +15137,7 @@
       <c r="X66" s="35"/>
       <c r="Y66" s="35"/>
     </row>
-    <row r="67" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="44"/>
       <c r="B67" s="45"/>
       <c r="C67" s="46" t="s">
@@ -15104,7 +15166,7 @@
       <c r="X67" s="35"/>
       <c r="Y67" s="35"/>
     </row>
-    <row r="68" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="44"/>
       <c r="B68" s="52"/>
       <c r="C68" s="53" t="s">
@@ -15133,7 +15195,7 @@
       <c r="X68" s="35"/>
       <c r="Y68" s="35"/>
     </row>
-    <row r="69" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="44"/>
       <c r="B69" s="45"/>
       <c r="C69" s="53" t="s">
@@ -15220,7 +15282,7 @@
       <c r="X71" s="35"/>
       <c r="Y71" s="35"/>
     </row>
-    <row r="72" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="44"/>
       <c r="B72" s="52"/>
       <c r="C72" s="64" t="s">
@@ -15249,7 +15311,7 @@
       <c r="X72" s="35"/>
       <c r="Y72" s="35"/>
     </row>
-    <row r="73" ht="10.95" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="12.2" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="70"/>
       <c r="B73" s="56"/>
       <c r="C73" s="57" t="s">
@@ -15279,7 +15341,7 @@
       <c r="Y73" s="35"/>
     </row>
     <row r="74" ht="12.75" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="76"/>
+      <c r="A74" s="559"/>
       <c r="B74" s="45"/>
       <c r="C74" s="64" t="s">
         <v>18</v>
@@ -15308,7 +15370,7 @@
       <c r="Y74" s="35"/>
     </row>
     <row r="75" ht="12.75" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="76"/>
+      <c r="A75" s="559"/>
       <c r="B75" s="77"/>
       <c r="C75" s="53" t="s">
         <v>19</v>
@@ -15337,7 +15399,7 @@
       <c r="Y75" s="35"/>
     </row>
     <row r="76" ht="12.75" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="76"/>
+      <c r="A76" s="559"/>
       <c r="B76" s="77"/>
       <c r="C76" s="53" t="s">
         <v>18</v>
@@ -15366,7 +15428,7 @@
       <c r="Y76" s="35"/>
     </row>
     <row r="77" ht="12.75" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="76"/>
+      <c r="A77" s="559"/>
       <c r="B77" s="77"/>
       <c r="C77" s="53" t="s">
         <v>19</v>
@@ -15395,7 +15457,7 @@
       <c r="Y77" s="35"/>
     </row>
     <row r="78" ht="12.75" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="76"/>
+      <c r="A78" s="559"/>
       <c r="B78" s="77"/>
       <c r="C78" s="53" t="s">
         <v>18</v>
@@ -15424,7 +15486,7 @@
       <c r="Y78" s="35"/>
     </row>
     <row r="79" ht="12.75" customHeight="1" hidden="1" spans="1:25" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="76"/>
+      <c r="A79" s="559"/>
       <c r="B79" s="77"/>
       <c r="C79" s="53" t="s">
         <v>19</v>
@@ -15607,7 +15669,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" ht="13.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="83" ht="14.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="99" t="s">
         <v>21</v>
       </c>
@@ -16083,7 +16145,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF993300"/>
   </sheetPr>
@@ -16877,7 +16939,7 @@
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="175" t="s">
+      <c r="B6" s="138" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -16887,13 +16949,13 @@
       <c r="G6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="158"/>
+      <c r="H6" s="138"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="176"/>
+      <c r="L6" s="572"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -16939,7 +17001,7 @@
       <c r="A8" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="573" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="3"/>
@@ -16949,13 +17011,13 @@
       <c r="G8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="158"/>
+      <c r="H8" s="138"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="175" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="158"/>
+      <c r="L8" s="138"/>
       <c r="M8" s="158"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -16997,7 +17059,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="177" t="s">
         <v>45</v>
       </c>
@@ -17042,7 +17104,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="181"/>
       <c r="C11" s="181"/>
@@ -17072,19 +17134,19 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="183"/>
+      <c r="A12" s="574"/>
       <c r="B12" s="184"/>
       <c r="C12" s="185"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="188"/>
+      <c r="D12" s="575"/>
+      <c r="E12" s="576"/>
+      <c r="F12" s="577"/>
       <c r="G12" s="189"/>
       <c r="H12" s="190"/>
       <c r="I12" s="191"/>
       <c r="J12" s="192"/>
       <c r="K12" s="189"/>
       <c r="L12" s="189"/>
-      <c r="M12" s="193"/>
+      <c r="M12" s="578"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -17099,19 +17161,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="194"/>
+      <c r="A13" s="579"/>
       <c r="B13" s="195"/>
       <c r="C13" s="195"/>
-      <c r="D13" s="196"/>
-      <c r="E13" s="197"/>
-      <c r="F13" s="198"/>
+      <c r="D13" s="580"/>
+      <c r="E13" s="581"/>
+      <c r="F13" s="582"/>
       <c r="G13" s="195"/>
       <c r="H13" s="199"/>
       <c r="I13" s="200"/>
       <c r="J13" s="199"/>
       <c r="K13" s="195"/>
       <c r="L13" s="195"/>
-      <c r="M13" s="201"/>
+      <c r="M13" s="583"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -17126,19 +17188,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="194"/>
+      <c r="A14" s="579"/>
       <c r="B14" s="195"/>
       <c r="C14" s="195"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="197"/>
-      <c r="F14" s="198"/>
+      <c r="D14" s="580"/>
+      <c r="E14" s="581"/>
+      <c r="F14" s="582"/>
       <c r="G14" s="195"/>
       <c r="H14" s="199"/>
       <c r="I14" s="200"/>
       <c r="J14" s="199"/>
       <c r="K14" s="195"/>
       <c r="L14" s="195"/>
-      <c r="M14" s="202"/>
+      <c r="M14" s="584"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -17153,19 +17215,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="194"/>
+      <c r="A15" s="579"/>
       <c r="B15" s="195"/>
       <c r="C15" s="195"/>
-      <c r="D15" s="196"/>
-      <c r="E15" s="197"/>
-      <c r="F15" s="198"/>
+      <c r="D15" s="580"/>
+      <c r="E15" s="581"/>
+      <c r="F15" s="582"/>
       <c r="G15" s="195"/>
       <c r="H15" s="199"/>
       <c r="I15" s="200"/>
       <c r="J15" s="199"/>
       <c r="K15" s="195"/>
       <c r="L15" s="195"/>
-      <c r="M15" s="201"/>
+      <c r="M15" s="583"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -17180,19 +17242,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="194"/>
+      <c r="A16" s="579"/>
       <c r="B16" s="195"/>
       <c r="C16" s="195"/>
-      <c r="D16" s="196"/>
-      <c r="E16" s="197"/>
-      <c r="F16" s="198"/>
+      <c r="D16" s="580"/>
+      <c r="E16" s="581"/>
+      <c r="F16" s="582"/>
       <c r="G16" s="195"/>
       <c r="H16" s="199"/>
       <c r="I16" s="200"/>
       <c r="J16" s="199"/>
       <c r="K16" s="195"/>
       <c r="L16" s="195"/>
-      <c r="M16" s="202"/>
+      <c r="M16" s="584"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -17207,19 +17269,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="203"/>
+      <c r="A17" s="585"/>
       <c r="B17" s="204"/>
       <c r="C17" s="146"/>
-      <c r="D17" s="196"/>
-      <c r="E17" s="197"/>
-      <c r="F17" s="198"/>
+      <c r="D17" s="580"/>
+      <c r="E17" s="581"/>
+      <c r="F17" s="582"/>
       <c r="G17" s="195"/>
       <c r="H17" s="205"/>
       <c r="I17" s="206"/>
       <c r="J17" s="199"/>
       <c r="K17" s="195"/>
       <c r="L17" s="195"/>
-      <c r="M17" s="207"/>
+      <c r="M17" s="586"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -17234,19 +17296,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="17.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="203"/>
+      <c r="A18" s="585"/>
       <c r="B18" s="204"/>
       <c r="C18" s="146"/>
-      <c r="D18" s="196"/>
-      <c r="E18" s="197"/>
-      <c r="F18" s="198"/>
+      <c r="D18" s="580"/>
+      <c r="E18" s="581"/>
+      <c r="F18" s="582"/>
       <c r="G18" s="195"/>
       <c r="H18" s="205"/>
       <c r="I18" s="206"/>
       <c r="J18" s="199"/>
       <c r="K18" s="195"/>
       <c r="L18" s="195"/>
-      <c r="M18" s="207"/>
+      <c r="M18" s="586"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -17958,7 +18020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF333300"/>
   </sheetPr>
@@ -18751,7 +18813,7 @@
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="175" t="s">
+      <c r="B6" s="138" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -18761,13 +18823,13 @@
       <c r="G6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="158"/>
+      <c r="H6" s="138"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="176"/>
+      <c r="L6" s="572"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -18813,7 +18875,7 @@
       <c r="A8" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="573" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="3"/>
@@ -18823,13 +18885,13 @@
       <c r="G8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="158"/>
+      <c r="H8" s="138"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="175" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="158"/>
+      <c r="L8" s="138"/>
       <c r="M8" s="158"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -18871,7 +18933,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="177" t="s">
         <v>45</v>
       </c>
@@ -18916,7 +18978,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
       <c r="B11" s="181"/>
       <c r="C11" s="181"/>
@@ -18946,19 +19008,19 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="183"/>
+      <c r="A12" s="574"/>
       <c r="B12" s="189"/>
       <c r="C12" s="189"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="188"/>
+      <c r="D12" s="575"/>
+      <c r="E12" s="576"/>
+      <c r="F12" s="577"/>
       <c r="G12" s="189"/>
       <c r="H12" s="192"/>
       <c r="I12" s="242"/>
       <c r="J12" s="192"/>
       <c r="K12" s="189"/>
       <c r="L12" s="189"/>
-      <c r="M12" s="243"/>
+      <c r="M12" s="587"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -18973,19 +19035,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="194"/>
+      <c r="A13" s="579"/>
       <c r="B13" s="195"/>
       <c r="C13" s="195"/>
-      <c r="D13" s="196"/>
-      <c r="E13" s="197"/>
-      <c r="F13" s="198"/>
+      <c r="D13" s="580"/>
+      <c r="E13" s="581"/>
+      <c r="F13" s="582"/>
       <c r="G13" s="195"/>
       <c r="H13" s="199"/>
       <c r="I13" s="200"/>
       <c r="J13" s="199"/>
       <c r="K13" s="195"/>
       <c r="L13" s="195"/>
-      <c r="M13" s="201"/>
+      <c r="M13" s="583"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -19000,19 +19062,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="17.1" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="194"/>
+      <c r="A14" s="579"/>
       <c r="B14" s="195"/>
       <c r="C14" s="195"/>
-      <c r="D14" s="196"/>
-      <c r="E14" s="197"/>
-      <c r="F14" s="198"/>
+      <c r="D14" s="580"/>
+      <c r="E14" s="581"/>
+      <c r="F14" s="582"/>
       <c r="G14" s="195"/>
       <c r="H14" s="199"/>
       <c r="I14" s="200"/>
       <c r="J14" s="199"/>
       <c r="K14" s="195"/>
       <c r="L14" s="195"/>
-      <c r="M14" s="201"/>
+      <c r="M14" s="583"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -19027,19 +19089,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="17.1" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="194"/>
+      <c r="A15" s="579"/>
       <c r="B15" s="195"/>
       <c r="C15" s="195"/>
-      <c r="D15" s="196"/>
-      <c r="E15" s="197"/>
-      <c r="F15" s="198"/>
+      <c r="D15" s="580"/>
+      <c r="E15" s="581"/>
+      <c r="F15" s="582"/>
       <c r="G15" s="195"/>
       <c r="H15" s="199"/>
       <c r="I15" s="200"/>
       <c r="J15" s="199"/>
       <c r="K15" s="195"/>
       <c r="L15" s="195"/>
-      <c r="M15" s="201"/>
+      <c r="M15" s="583"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -19054,19 +19116,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="194"/>
+      <c r="A16" s="579"/>
       <c r="B16" s="195"/>
       <c r="C16" s="195"/>
-      <c r="D16" s="196"/>
-      <c r="E16" s="197"/>
-      <c r="F16" s="198"/>
+      <c r="D16" s="580"/>
+      <c r="E16" s="581"/>
+      <c r="F16" s="582"/>
       <c r="G16" s="195"/>
       <c r="H16" s="199"/>
       <c r="I16" s="200"/>
       <c r="J16" s="199"/>
       <c r="K16" s="195"/>
       <c r="L16" s="195"/>
-      <c r="M16" s="201"/>
+      <c r="M16" s="583"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -19081,19 +19143,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="194"/>
+      <c r="A17" s="579"/>
       <c r="B17" s="195"/>
       <c r="C17" s="195"/>
-      <c r="D17" s="196"/>
-      <c r="E17" s="197"/>
-      <c r="F17" s="198"/>
+      <c r="D17" s="580"/>
+      <c r="E17" s="581"/>
+      <c r="F17" s="582"/>
       <c r="G17" s="195"/>
       <c r="H17" s="199"/>
       <c r="I17" s="200"/>
       <c r="J17" s="199"/>
       <c r="K17" s="195"/>
       <c r="L17" s="195"/>
-      <c r="M17" s="201"/>
+      <c r="M17" s="583"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -19108,19 +19170,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="194"/>
+      <c r="A18" s="579"/>
       <c r="B18" s="195"/>
       <c r="C18" s="195"/>
-      <c r="D18" s="196"/>
-      <c r="E18" s="197"/>
-      <c r="F18" s="198"/>
+      <c r="D18" s="580"/>
+      <c r="E18" s="581"/>
+      <c r="F18" s="582"/>
       <c r="G18" s="195"/>
       <c r="H18" s="199"/>
       <c r="I18" s="200"/>
       <c r="J18" s="199"/>
       <c r="K18" s="195"/>
       <c r="L18" s="195"/>
-      <c r="M18" s="201"/>
+      <c r="M18" s="583"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -19135,19 +19197,19 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="194"/>
+      <c r="A19" s="579"/>
       <c r="B19" s="195"/>
       <c r="C19" s="195"/>
-      <c r="D19" s="196"/>
-      <c r="E19" s="197"/>
-      <c r="F19" s="198"/>
+      <c r="D19" s="580"/>
+      <c r="E19" s="581"/>
+      <c r="F19" s="582"/>
       <c r="G19" s="195"/>
       <c r="H19" s="199"/>
       <c r="I19" s="200"/>
       <c r="J19" s="199"/>
       <c r="K19" s="195"/>
       <c r="L19" s="195"/>
-      <c r="M19" s="201"/>
+      <c r="M19" s="583"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -19162,19 +19224,19 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="194"/>
+      <c r="A20" s="579"/>
       <c r="B20" s="195"/>
       <c r="C20" s="195"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="197"/>
-      <c r="F20" s="198"/>
+      <c r="D20" s="580"/>
+      <c r="E20" s="581"/>
+      <c r="F20" s="582"/>
       <c r="G20" s="195"/>
       <c r="H20" s="199"/>
       <c r="I20" s="200"/>
       <c r="J20" s="199"/>
       <c r="K20" s="195"/>
       <c r="L20" s="195"/>
-      <c r="M20" s="244"/>
+      <c r="M20" s="588"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -19189,19 +19251,19 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="194"/>
+      <c r="A21" s="579"/>
       <c r="B21" s="195"/>
       <c r="C21" s="195"/>
-      <c r="D21" s="196"/>
-      <c r="E21" s="197"/>
-      <c r="F21" s="198"/>
+      <c r="D21" s="580"/>
+      <c r="E21" s="581"/>
+      <c r="F21" s="582"/>
       <c r="G21" s="195"/>
       <c r="H21" s="199"/>
       <c r="I21" s="200"/>
       <c r="J21" s="199"/>
       <c r="K21" s="195"/>
       <c r="L21" s="195"/>
-      <c r="M21" s="244"/>
+      <c r="M21" s="588"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -19216,19 +19278,19 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="194"/>
+      <c r="A22" s="579"/>
       <c r="B22" s="195"/>
       <c r="C22" s="195"/>
-      <c r="D22" s="196"/>
-      <c r="E22" s="197"/>
-      <c r="F22" s="198"/>
+      <c r="D22" s="580"/>
+      <c r="E22" s="581"/>
+      <c r="F22" s="582"/>
       <c r="G22" s="195"/>
       <c r="H22" s="199"/>
       <c r="I22" s="200"/>
       <c r="J22" s="199"/>
       <c r="K22" s="195"/>
       <c r="L22" s="195"/>
-      <c r="M22" s="244"/>
+      <c r="M22" s="588"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -19243,19 +19305,19 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23" ht="17.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="194"/>
+      <c r="A23" s="579"/>
       <c r="B23" s="195"/>
       <c r="C23" s="195"/>
-      <c r="D23" s="196"/>
-      <c r="E23" s="197"/>
-      <c r="F23" s="198"/>
+      <c r="D23" s="580"/>
+      <c r="E23" s="581"/>
+      <c r="F23" s="582"/>
       <c r="G23" s="195"/>
       <c r="H23" s="199"/>
       <c r="I23" s="200"/>
       <c r="J23" s="199"/>
       <c r="K23" s="195"/>
       <c r="L23" s="195"/>
-      <c r="M23" s="244"/>
+      <c r="M23" s="588"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -19270,19 +19332,19 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24" ht="17.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="194"/>
+      <c r="A24" s="579"/>
       <c r="B24" s="195"/>
       <c r="C24" s="195"/>
-      <c r="D24" s="196"/>
-      <c r="E24" s="197"/>
-      <c r="F24" s="198"/>
+      <c r="D24" s="580"/>
+      <c r="E24" s="581"/>
+      <c r="F24" s="582"/>
       <c r="G24" s="195"/>
       <c r="H24" s="199"/>
       <c r="I24" s="200"/>
       <c r="J24" s="199"/>
       <c r="K24" s="195"/>
       <c r="L24" s="195"/>
-      <c r="M24" s="244"/>
+      <c r="M24" s="588"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -19874,7 +19936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499954222235786"/>
   </sheetPr>
@@ -20520,7 +20582,7 @@
       <c r="A6" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="556"/>
       <c r="C6" s="9"/>
       <c r="D6" s="227" t="s">
         <v>3</v>
@@ -20538,7 +20600,7 @@
       <c r="O6" s="227" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="9"/>
+      <c r="P6" s="556"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="168" t="s">
         <v>144</v>
@@ -20554,7 +20616,7 @@
       </c>
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
-      <c r="AB6" s="413">
+      <c r="AB6" s="594">
         <v>46228</v>
       </c>
       <c r="AC6" s="13"/>
@@ -20608,7 +20670,7 @@
       <c r="A8" s="414" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="9"/>
+      <c r="B8" s="556"/>
       <c r="C8" s="9"/>
       <c r="D8" s="415" t="s">
         <v>67</v>
@@ -20626,7 +20688,7 @@
       <c r="O8" s="415" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="9"/>
+      <c r="P8" s="556"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="416">
         <v>8</v>
@@ -20642,7 +20704,7 @@
       </c>
       <c r="Z8" s="13"/>
       <c r="AA8" s="13"/>
-      <c r="AB8" s="416" t="s">
+      <c r="AB8" s="595" t="s">
         <v>26</v>
       </c>
       <c r="AC8" s="13"/>
@@ -24171,7 +24233,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y47"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -24835,17 +24897,17 @@
       <c r="A6" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="126"/>
+      <c r="B6" s="560"/>
       <c r="C6" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="128"/>
+      <c r="D6" s="561"/>
       <c r="E6" s="128"/>
       <c r="F6" s="9"/>
       <c r="G6" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="130">
+      <c r="H6" s="562">
         <v>46228</v>
       </c>
       <c r="I6" s="9"/>
@@ -24897,17 +24959,17 @@
       <c r="A8" s="125" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="125"/>
+      <c r="B8" s="561"/>
       <c r="C8" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="128"/>
+      <c r="D8" s="561"/>
       <c r="E8" s="128"/>
       <c r="F8" s="127"/>
       <c r="G8" s="131" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="15"/>
+      <c r="H8" s="563"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -25045,7 +25107,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="136"/>
-      <c r="C13" s="137"/>
+      <c r="C13" s="564"/>
       <c r="D13" s="137"/>
       <c r="E13" s="137"/>
       <c r="F13" s="137"/>
@@ -25072,7 +25134,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="139"/>
       <c r="B14" s="140"/>
-      <c r="C14" s="141"/>
+      <c r="C14" s="565"/>
       <c r="D14" s="141"/>
       <c r="E14" s="141"/>
       <c r="F14" s="141"/>
@@ -25099,7 +25161,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="139"/>
       <c r="B15" s="142"/>
-      <c r="C15" s="143"/>
+      <c r="C15" s="566"/>
       <c r="D15" s="144"/>
       <c r="E15" s="144"/>
       <c r="F15" s="144"/>
@@ -25126,7 +25188,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="139"/>
       <c r="B16" s="146"/>
-      <c r="C16" s="147"/>
+      <c r="C16" s="567"/>
       <c r="D16" s="147"/>
       <c r="E16" s="147"/>
       <c r="F16" s="147"/>
@@ -25153,7 +25215,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="148"/>
       <c r="B17" s="149"/>
-      <c r="C17" s="150"/>
+      <c r="C17" s="568"/>
       <c r="D17" s="150"/>
       <c r="E17" s="150"/>
       <c r="F17" s="150"/>
@@ -25182,7 +25244,7 @@
         <v>37</v>
       </c>
       <c r="B18" s="152"/>
-      <c r="C18" s="147"/>
+      <c r="C18" s="567"/>
       <c r="D18" s="147"/>
       <c r="E18" s="147"/>
       <c r="F18" s="147"/>
@@ -25209,7 +25271,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="153"/>
       <c r="B19" s="142"/>
-      <c r="C19" s="143"/>
+      <c r="C19" s="566"/>
       <c r="D19" s="144"/>
       <c r="E19" s="144"/>
       <c r="F19" s="144"/>
@@ -25236,7 +25298,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="139"/>
       <c r="B20" s="152"/>
-      <c r="C20" s="141"/>
+      <c r="C20" s="565"/>
       <c r="D20" s="141"/>
       <c r="E20" s="141"/>
       <c r="F20" s="141"/>
@@ -25263,7 +25325,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="154"/>
       <c r="B21" s="152"/>
-      <c r="C21" s="147"/>
+      <c r="C21" s="567"/>
       <c r="D21" s="147"/>
       <c r="E21" s="147"/>
       <c r="F21" s="147"/>
@@ -25290,7 +25352,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="155"/>
       <c r="B22" s="149"/>
-      <c r="C22" s="150"/>
+      <c r="C22" s="568"/>
       <c r="D22" s="150"/>
       <c r="E22" s="150"/>
       <c r="F22" s="150"/>
@@ -25317,7 +25379,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="156"/>
       <c r="B23" s="152"/>
-      <c r="C23" s="143"/>
+      <c r="C23" s="566"/>
       <c r="D23" s="144"/>
       <c r="E23" s="144"/>
       <c r="F23" s="144"/>
@@ -25344,7 +25406,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="157"/>
       <c r="B24" s="152"/>
-      <c r="C24" s="147"/>
+      <c r="C24" s="567"/>
       <c r="D24" s="147"/>
       <c r="E24" s="147"/>
       <c r="F24" s="147"/>
@@ -25371,7 +25433,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="159"/>
       <c r="B25" s="152"/>
-      <c r="C25" s="141"/>
+      <c r="C25" s="565"/>
       <c r="D25" s="141"/>
       <c r="E25" s="141"/>
       <c r="F25" s="141"/>
@@ -25398,7 +25460,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="139"/>
       <c r="B26" s="152"/>
-      <c r="C26" s="141"/>
+      <c r="C26" s="565"/>
       <c r="D26" s="141"/>
       <c r="E26" s="141"/>
       <c r="F26" s="141"/>
@@ -25425,7 +25487,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="148"/>
       <c r="B27" s="149"/>
-      <c r="C27" s="160"/>
+      <c r="C27" s="569"/>
       <c r="D27" s="160"/>
       <c r="E27" s="160"/>
       <c r="F27" s="160"/>
@@ -25452,7 +25514,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
       <c r="B28" s="152"/>
-      <c r="C28" s="147"/>
+      <c r="C28" s="567"/>
       <c r="D28" s="147"/>
       <c r="E28" s="147"/>
       <c r="F28" s="147"/>
@@ -25479,7 +25541,7 @@
     <row r="29" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="139"/>
       <c r="B29" s="152"/>
-      <c r="C29" s="143"/>
+      <c r="C29" s="566"/>
       <c r="D29" s="144"/>
       <c r="E29" s="144"/>
       <c r="F29" s="144"/>
@@ -25506,7 +25568,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="139"/>
       <c r="B30" s="152"/>
-      <c r="C30" s="147"/>
+      <c r="C30" s="567"/>
       <c r="D30" s="147"/>
       <c r="E30" s="147"/>
       <c r="F30" s="147"/>
@@ -25533,7 +25595,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="139"/>
       <c r="B31" s="142"/>
-      <c r="C31" s="143"/>
+      <c r="C31" s="566"/>
       <c r="D31" s="144"/>
       <c r="E31" s="144"/>
       <c r="F31" s="144"/>
@@ -25560,7 +25622,7 @@
     <row r="32" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="159"/>
       <c r="B32" s="149"/>
-      <c r="C32" s="150"/>
+      <c r="C32" s="568"/>
       <c r="D32" s="150"/>
       <c r="E32" s="150"/>
       <c r="F32" s="150"/>
@@ -25587,7 +25649,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
       <c r="B33" s="152"/>
-      <c r="C33" s="147"/>
+      <c r="C33" s="567"/>
       <c r="D33" s="147"/>
       <c r="E33" s="147"/>
       <c r="F33" s="147"/>
@@ -25614,7 +25676,7 @@
     <row r="34" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="139"/>
       <c r="B34" s="152"/>
-      <c r="C34" s="141"/>
+      <c r="C34" s="565"/>
       <c r="D34" s="141"/>
       <c r="E34" s="141"/>
       <c r="F34" s="141"/>
@@ -25641,7 +25703,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="161"/>
       <c r="B35" s="146"/>
-      <c r="C35" s="162"/>
+      <c r="C35" s="570"/>
       <c r="D35" s="144"/>
       <c r="E35" s="144"/>
       <c r="F35" s="144"/>
@@ -25668,7 +25730,7 @@
     <row r="36" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="163"/>
       <c r="B36" s="152"/>
-      <c r="C36" s="164"/>
+      <c r="C36" s="571"/>
       <c r="D36" s="165"/>
       <c r="E36" s="165"/>
       <c r="F36" s="165"/>
@@ -25695,7 +25757,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="167"/>
       <c r="B37" s="149"/>
-      <c r="C37" s="160"/>
+      <c r="C37" s="569"/>
       <c r="D37" s="160"/>
       <c r="E37" s="160"/>
       <c r="F37" s="160"/>
@@ -25992,7 +26054,7 @@
       <c r="Y47" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="37">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -26027,6 +26089,9 @@
     <mergeCell ref="C37:H37"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="G42:H42"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="C40:H40"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.4724409448818898" right="0.4724409448818898" top="0.5905511811023623" bottom="0.5118110236220472" header="0.5118110236220472" footer="0.35433070866141736"/>
@@ -26035,7 +26100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -26705,7 +26770,7 @@
       <c r="A4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="175" t="s">
+      <c r="B4" s="138" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="175"/>
@@ -26714,7 +26779,7 @@
       <c r="F4" s="267" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="176"/>
+      <c r="G4" s="572"/>
       <c r="H4" s="158"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -26765,7 +26830,7 @@
       <c r="A6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="158" t="s">
+      <c r="B6" s="138" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="158"/>
@@ -26776,7 +26841,7 @@
       <c r="F6" s="267" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="122" t="s">
+      <c r="G6" s="589" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="122"/>
@@ -27419,12 +27484,12 @@
     <row r="29" ht="24" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="310"/>
       <c r="B29" s="311"/>
-      <c r="C29" s="312"/>
-      <c r="D29" s="312"/>
-      <c r="E29" s="312"/>
-      <c r="F29" s="312"/>
-      <c r="G29" s="312"/>
-      <c r="H29" s="313"/>
+      <c r="C29" s="590"/>
+      <c r="D29" s="590"/>
+      <c r="E29" s="590"/>
+      <c r="F29" s="590"/>
+      <c r="G29" s="590"/>
+      <c r="H29" s="591"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -27446,12 +27511,12 @@
     <row r="30" ht="24" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="310"/>
       <c r="B30" s="311"/>
-      <c r="C30" s="312"/>
-      <c r="D30" s="312"/>
-      <c r="E30" s="312"/>
-      <c r="F30" s="312"/>
-      <c r="G30" s="312"/>
-      <c r="H30" s="313"/>
+      <c r="C30" s="590"/>
+      <c r="D30" s="590"/>
+      <c r="E30" s="590"/>
+      <c r="F30" s="590"/>
+      <c r="G30" s="590"/>
+      <c r="H30" s="591"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -27473,12 +27538,12 @@
     <row r="31" ht="24" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="314"/>
       <c r="B31" s="315"/>
-      <c r="C31" s="316"/>
-      <c r="D31" s="316"/>
-      <c r="E31" s="316"/>
-      <c r="F31" s="316"/>
-      <c r="G31" s="316"/>
-      <c r="H31" s="317"/>
+      <c r="C31" s="592"/>
+      <c r="D31" s="592"/>
+      <c r="E31" s="592"/>
+      <c r="F31" s="592"/>
+      <c r="G31" s="592"/>
+      <c r="H31" s="593"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -27777,7 +27842,7 @@
       <c r="F41" s="267" t="s">
         <v>82</v>
       </c>
-      <c r="G41" s="176">
+      <c r="G41" s="572">
         <v>46228</v>
       </c>
       <c r="H41" s="158"/>
@@ -27830,7 +27895,7 @@
       <c r="A43" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B43" s="158" t="s">
+      <c r="B43" s="138" t="s">
         <v>77</v>
       </c>
       <c r="C43" s="158"/>
@@ -27841,7 +27906,7 @@
       <c r="F43" s="267" t="s">
         <v>85</v>
       </c>
-      <c r="G43" s="122" t="s">
+      <c r="G43" s="589" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="122"/>
